--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -796,6 +796,332 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126287839</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Djupedals mosse, Djupedals mosse, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>306203</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6414510</v>
+      </c>
+      <c r="S3" t="n">
+        <v>15</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126287538</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Glöskär, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>306250</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6414440</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spillkråkehack och flera bihål i högstubbe. 4 st bohål syntes.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126287766</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57649</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Djupedals mosse, Djupedals mosse, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>306665</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6414521</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>126287839</v>
       </c>
       <c r="B3" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>126287538</v>
       </c>
       <c r="B4" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>126287766</v>
       </c>
       <c r="B5" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>126287839</v>
       </c>
       <c r="B3" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>126287538</v>
       </c>
       <c r="B4" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>126287766</v>
       </c>
       <c r="B5" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -1567,7 +1567,7 @@
         <v>126879253</v>
       </c>
       <c r="B10" t="n">
-        <v>95964</v>
+        <v>96039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -1567,7 +1567,7 @@
         <v>126879253</v>
       </c>
       <c r="B10" t="n">
-        <v>96039</v>
+        <v>96045</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -1567,7 +1567,7 @@
         <v>126879253</v>
       </c>
       <c r="B10" t="n">
-        <v>96045</v>
+        <v>96046</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -1128,7 +1128,7 @@
         <v>126879218</v>
       </c>
       <c r="B6" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>126879304</v>
       </c>
       <c r="B7" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>126878843</v>
       </c>
       <c r="B8" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>126879093</v>
       </c>
       <c r="B9" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>126879253</v>
       </c>
       <c r="B10" t="n">
-        <v>96046</v>
+        <v>96050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -1128,7 +1128,7 @@
         <v>126879218</v>
       </c>
       <c r="B6" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>126879304</v>
       </c>
       <c r="B7" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>126878843</v>
       </c>
       <c r="B8" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>126879093</v>
       </c>
       <c r="B9" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>126879253</v>
       </c>
       <c r="B10" t="n">
-        <v>96050</v>
+        <v>96052</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1669,6 +1669,653 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128100016</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97094</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Glöskär, Glöskär, Boh</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>306623</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6414564</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128099460</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Djupedals mosse, Djupedals mosse, Boh</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>306498</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6414538</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128099860</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Glöskär, Glöskär, Boh</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>306585</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6414552</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128099768</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97094</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Glöskär, Glöskär, Boh</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>306586</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6414555</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:47</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128101018</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Glöskär, Glöskär, Boh</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>306227</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6414439</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128098190</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57669</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Glöskär, Glöskär, Boh</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>306344</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6414572</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:49</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Inka Eriksson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -1674,7 +1674,7 @@
         <v>128100016</v>
       </c>
       <c r="B11" t="n">
-        <v>97094</v>
+        <v>97095</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128099768</v>
       </c>
       <c r="B14" t="n">
-        <v>97094</v>
+        <v>97095</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -1674,7 +1674,7 @@
         <v>128100016</v>
       </c>
       <c r="B11" t="n">
-        <v>97095</v>
+        <v>97096</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128099768</v>
       </c>
       <c r="B14" t="n">
-        <v>97095</v>
+        <v>97096</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -1674,7 +1674,7 @@
         <v>128100016</v>
       </c>
       <c r="B11" t="n">
-        <v>97096</v>
+        <v>97097</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128099768</v>
       </c>
       <c r="B14" t="n">
-        <v>97096</v>
+        <v>97097</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -1674,7 +1674,7 @@
         <v>128100016</v>
       </c>
       <c r="B11" t="n">
-        <v>97097</v>
+        <v>97105</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>128099460</v>
       </c>
       <c r="B12" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>128099860</v>
       </c>
       <c r="B13" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128099768</v>
       </c>
       <c r="B14" t="n">
-        <v>97097</v>
+        <v>97105</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>128101018</v>
       </c>
       <c r="B15" t="n">
-        <v>57685</v>
+        <v>57686</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>128098190</v>
       </c>
       <c r="B16" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -1674,7 +1674,7 @@
         <v>128100016</v>
       </c>
       <c r="B11" t="n">
-        <v>97105</v>
+        <v>97198</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>128099460</v>
       </c>
       <c r="B12" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>128099860</v>
       </c>
       <c r="B13" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128099768</v>
       </c>
       <c r="B14" t="n">
-        <v>97105</v>
+        <v>97198</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>128101018</v>
       </c>
       <c r="B15" t="n">
-        <v>57686</v>
+        <v>57698</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>128098190</v>
       </c>
       <c r="B16" t="n">
-        <v>57670</v>
+        <v>57682</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -1674,7 +1674,7 @@
         <v>128100016</v>
       </c>
       <c r="B11" t="n">
-        <v>97198</v>
+        <v>97210</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>128099460</v>
       </c>
       <c r="B12" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>128099860</v>
       </c>
       <c r="B13" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128099768</v>
       </c>
       <c r="B14" t="n">
-        <v>97198</v>
+        <v>97210</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>128101018</v>
       </c>
       <c r="B15" t="n">
-        <v>57698</v>
+        <v>57702</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>128098190</v>
       </c>
       <c r="B16" t="n">
-        <v>57682</v>
+        <v>57686</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -1674,7 +1674,7 @@
         <v>128100016</v>
       </c>
       <c r="B11" t="n">
-        <v>97210</v>
+        <v>97212</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>128099768</v>
       </c>
       <c r="B14" t="n">
-        <v>97210</v>
+        <v>97212</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -1128,7 +1128,7 @@
         <v>126879218</v>
       </c>
       <c r="B6" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>126879304</v>
       </c>
       <c r="B7" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>126878843</v>
       </c>
       <c r="B8" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>126879093</v>
       </c>
       <c r="B9" t="n">
-        <v>58033</v>
+        <v>58027</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>126879253</v>
       </c>
       <c r="B10" t="n">
-        <v>96052</v>
+        <v>96039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -1128,7 +1128,7 @@
         <v>126879218</v>
       </c>
       <c r="B6" t="n">
-        <v>57654</v>
+        <v>57660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>126879304</v>
       </c>
       <c r="B7" t="n">
-        <v>57654</v>
+        <v>57660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>126878843</v>
       </c>
       <c r="B8" t="n">
-        <v>57654</v>
+        <v>57660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>126879093</v>
       </c>
       <c r="B9" t="n">
-        <v>58027</v>
+        <v>58033</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>126879253</v>
       </c>
       <c r="B10" t="n">
-        <v>96039</v>
+        <v>96052</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111667662</v>
+        <v>126879253</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Djupedals mosse, Boh</t>
+          <t>Glöskär, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>306615</v>
+        <v>306538</v>
       </c>
       <c r="R2" t="n">
-        <v>6414592</v>
+        <v>6414717</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>18:45</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>18:45</t>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ca 40cm i omkrets</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,66 +763,67 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Lundström</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Lundström</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126287839</v>
+        <v>128099768</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djupedals mosse, Djupedals mosse, Boh</t>
+          <t>Glöskär, Glöskär, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>306203</v>
+        <v>306586</v>
       </c>
       <c r="R3" t="n">
-        <v>6414510</v>
+        <v>6414555</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,45 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126287538</v>
+        <v>128100016</v>
       </c>
       <c r="B4" t="n">
-        <v>57654</v>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Glöskär, Boh</t>
+          <t>Glöskär, Glöskär, Boh</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>306250</v>
+        <v>306623</v>
       </c>
       <c r="R4" t="n">
-        <v>6414440</v>
+        <v>6414564</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,27 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:47</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spillkråkehack och flera bihål i högstubbe. 4 st bohål syntes.</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,48 +996,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126287766</v>
+        <v>126288041</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>96348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupedals mosse, Djupedals mosse, Boh</t>
+          <t>Glöskär, Glöskär, Boh</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>306665</v>
+        <v>306151</v>
       </c>
       <c r="R5" t="n">
-        <v>6414521</v>
+        <v>6414632</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1088,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1098,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126879218</v>
+        <v>128101018</v>
       </c>
       <c r="B6" t="n">
-        <v>57660</v>
+        <v>57966</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,16 +1114,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1154,27 +1132,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Glöskär, Boh</t>
+          <t>Glöskär, Glöskär, Boh</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>306476</v>
+        <v>306227</v>
       </c>
       <c r="R6" t="n">
-        <v>6414663</v>
+        <v>6414439</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,17 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spår av födosökande spillkråka</t>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,26 +1198,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126879304</v>
+        <v>111667662</v>
       </c>
       <c r="B7" t="n">
-        <v>57660</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1263,28 +1238,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>nyligen använt bo</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Glöskär, Boh</t>
+          <t>Djupedals mosse, Boh</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>306543</v>
+        <v>306615</v>
       </c>
       <c r="R7" t="n">
-        <v>6414711</v>
+        <v>6414592</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1308,17 +1287,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2023-08-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Lite äldre spår av födosökande spilkråka</t>
+          <t>2023-08-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,26 +1317,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Magnus Lundström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Magnus Lundström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126878843</v>
+        <v>126287538</v>
       </c>
       <c r="B8" t="n">
-        <v>57660</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1373,29 +1357,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Glöskär, Boh</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>306225</v>
+        <v>306250</v>
       </c>
       <c r="R8" t="n">
-        <v>6414562</v>
+        <v>6414440</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,17 +1394,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Såg och hörde kråkan (spillkråkan alltså)</t>
+          <t>Spillkråkehack och flera bihål i högstubbe. 4 st bohål syntes.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1447,22 +1429,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126879093</v>
+        <v>126287766</v>
       </c>
       <c r="B9" t="n">
-        <v>58033</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,16 +1452,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1488,24 +1470,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Glöskär, Boh</t>
+          <t>Djupedals mosse, Djupedals mosse, Boh</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>306286</v>
+        <v>306665</v>
       </c>
       <c r="R9" t="n">
-        <v>6414430</v>
+        <v>6414521</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,12 +1506,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1552,22 +1536,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126879253</v>
+        <v>126287839</v>
       </c>
       <c r="B10" t="n">
-        <v>96052</v>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1575,41 +1559,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Glöskär, Boh</t>
+          <t>Djupedals mosse, Djupedals mosse, Boh</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>306538</v>
+        <v>306203</v>
       </c>
       <c r="R10" t="n">
-        <v>6414717</v>
+        <v>6414510</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1633,17 +1613,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>ca 40cm i omkrets</t>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,29 +1637,28 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linus Lundin</t>
+          <t>Inka Eriksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128100016</v>
+        <v>126878843</v>
       </c>
       <c r="B11" t="n">
-        <v>97212</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1682,34 +1666,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Glöskär, Glöskär, Boh</t>
+          <t>Glöskär, Boh</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>306623</v>
+        <v>306225</v>
       </c>
       <c r="R11" t="n">
-        <v>6414564</v>
+        <v>6414562</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1736,22 +1732,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:56</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:56</t>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Såg och hörde kråkan (spillkråkan alltså)</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1766,26 +1757,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128099460</v>
+        <v>126879218</v>
       </c>
       <c r="B12" t="n">
-        <v>57686</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1807,19 +1798,27 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupedals mosse, Djupedals mosse, Boh</t>
+          <t>Glöskär, Boh</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>306498</v>
+        <v>306476</v>
       </c>
       <c r="R12" t="n">
-        <v>6414538</v>
+        <v>6414663</v>
       </c>
       <c r="S12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1843,27 +1842,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:26</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Spår av födosökande spillkråka</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1878,26 +1867,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mats Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128099860</v>
+        <v>126879304</v>
       </c>
       <c r="B13" t="n">
-        <v>57686</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1919,19 +1908,27 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Glöskär, Glöskär, Boh</t>
+          <t>Glöskär, Boh</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>306585</v>
+        <v>306543</v>
       </c>
       <c r="R13" t="n">
-        <v>6414552</v>
+        <v>6414711</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1955,22 +1952,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:50</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:50</t>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Lite äldre spår av födosökande spilkråka</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1985,22 +1977,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128099768</v>
+        <v>128098190</v>
       </c>
       <c r="B14" t="n">
-        <v>97212</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2008,21 +2000,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2032,13 +2024,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>306586</v>
+        <v>306344</v>
       </c>
       <c r="R14" t="n">
-        <v>6414555</v>
+        <v>6414572</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2067,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2077,7 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,27 +2096,27 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128101018</v>
+        <v>128099460</v>
       </c>
       <c r="B15" t="n">
-        <v>57702</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100048</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2135,17 +2127,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Glöskär, Glöskär, Boh</t>
+          <t>Djupedals mosse, Djupedals mosse, Boh</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>306227</v>
+        <v>306498</v>
       </c>
       <c r="R15" t="n">
-        <v>6414439</v>
+        <v>6414538</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2174,7 +2166,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2184,7 +2176,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,26 +2196,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Inka Eriksson</t>
+          <t>Mats Eriksson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128098190</v>
+        <v>128099860</v>
       </c>
       <c r="B16" t="n">
-        <v>57686</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2246,13 +2243,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>306344</v>
+        <v>306585</v>
       </c>
       <c r="R16" t="n">
-        <v>6414572</v>
+        <v>6414552</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2281,7 +2278,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2291,7 +2288,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2315,6 +2312,111 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126879093</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Glöskär, Boh</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>306286</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6414430</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kungälv</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34725-2024 artfynd.xlsx
+++ b/artfynd/A 34725-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126879253</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128099768</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128100016</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126288041</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128101018</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111667662</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,6 +1473,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126287538</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1545,6 +1585,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126287766</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1652,6 +1697,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126287839</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1766,6 +1816,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126878843</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1876,6 +1931,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126879218</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1986,6 +2046,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126879304</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2093,6 +2158,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128098190</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2205,6 +2275,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128099460</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2312,6 +2387,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128099860</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2417,8 +2497,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126879093</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>